--- a/docs/base_datos.xlsx
+++ b/docs/base_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9cd9fa3079768ea/Desktop/CONFIRMACION PREVIA/backend/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{A069D832-941B-4A69-9AFD-A62A51A2887A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89E619E1-DE19-4315-B710-9088036C6449}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{A069D832-941B-4A69-9AFD-A62A51A2887A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99BEC59D-7659-48A4-8CB1-F59397920035}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{203DBCE0-566D-42E5-8A51-BDC7143FE5DE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="187">
   <si>
     <t> Cliente</t>
   </si>
@@ -33,24 +33,15 @@
     <t> Fecha de programación desde</t>
   </si>
   <si>
-    <t>Ibarra_HFC</t>
-  </si>
-  <si>
     <t>ISERIBA-38 MANTE IBA GPON Z0 | UMAQUINGA CRIOLLO MATEO GABRIEL (Tecnico)</t>
   </si>
   <si>
-    <t>QUITO</t>
-  </si>
-  <si>
     <t>ISERTEL-60 UIO GPON Z2.3 CH | VEGA MANOBANDA EDISON (Tecnico)</t>
   </si>
   <si>
     <t>ISERTEL-117 UIO GPON Z1.3.2 PL| IBAZA MOLINA EDISON DARWIN (Tecnico)</t>
   </si>
   <si>
-    <t>Ambato_HFC</t>
-  </si>
-  <si>
     <t>ISERTEL-135 UIO GPON Z2.1 FRR | PILLAJO CHASIPANTA BRYAN DAVID (Tecnico)</t>
   </si>
   <si>
@@ -72,9 +63,6 @@
     <t>ISERTEL-75 UIO GPON Z1.5 C | CAIZA CHULDE ERICK (Tecnico)</t>
   </si>
   <si>
-    <t>Riobamba_HFC</t>
-  </si>
-  <si>
     <t>ISERRIO-23 RIO/COL GPON Z1 | LOPEZ SHUNTA LUIS (Tecnico)</t>
   </si>
   <si>
@@ -99,9 +87,6 @@
     <t>ISERIBA-36 MANTE OTA-CAY Z0 | CUALCHI COLLAGUAZO JUAN ARMANDO (Tecnico)</t>
   </si>
   <si>
-    <t>Guayaquil_HFC</t>
-  </si>
-  <si>
     <t>ISERTEL-114 QUEV MANT Z0 | LUNA SANCHEZ BRYAN (Tecnico)</t>
   </si>
   <si>
@@ -114,6 +99,9 @@
     <t>ORDER/446236/2026</t>
   </si>
   <si>
+    <t>Quito, Lizardo Ruiz, COTOCOLLAO LIZARDO RUIZ,S/N, BACHILLER GUEVARA ,, , LIZARDO RUIZ OE4563 Y BACHILLER GUEVARA CASA ESQUINA -78.49253,-0.1139133,1Q,1Q-3 , (-0.1139133/-78.49253)</t>
+  </si>
+  <si>
     <t>PAUCAR CRIOLLO JOSE MARIANO</t>
   </si>
   <si>
@@ -123,6 +111,9 @@
     <t>ORDER/454967/2026</t>
   </si>
   <si>
+    <t>Ambato, Las Americas, INGAHURCO LAS AMERICAS,, COLOMBIA ,, , -78.61769104,-1.2324792147,1T,1T-e , (-1.2324792147/-78.61769104)</t>
+  </si>
+  <si>
     <t>DAVALOS AGUIRRE FLAVIO ROBERTO</t>
   </si>
   <si>
@@ -132,6 +123,9 @@
     <t>ORDER/454947/2026</t>
   </si>
   <si>
+    <t>Riobamba, Av. 9 De Octubre, LA JOYA AV. 9 DE OCTUBRE,Villa 0, GARCIA MORENO ,P, Dp,Mz Oficina de un piso esquinera de cubierta -78.657383,-1.67845,RB4W, , (-1.67845/-78.657383)</t>
+  </si>
+  <si>
     <t>VELASCO TENE CRISTIAN ROGEL</t>
   </si>
   <si>
@@ -141,6 +135,9 @@
     <t>ORDER/454918/2026</t>
   </si>
   <si>
+    <t>Quevedo, Bolivar, CENTRO BOLIVAR,Villa 1, CALLE 6A ,P, Dp,Mz Casa dos pisos color blanco y amarillo y tejas en los valcones en la planta baja hay un cyber. Que -79.465866,-1.024746,QV2AJ,QV2HA16 , (-1.024746/-79.465866)</t>
+  </si>
+  <si>
     <t>TRAVEZ ZAMBRANO CARLOS ALBERTO</t>
   </si>
   <si>
@@ -150,6 +147,9 @@
     <t>ORDER/454890/2026</t>
   </si>
   <si>
+    <t>Riobamba, Alfredo Pareja, RIOBAMBA NORTE II ALFREDO PAREJA,Villa Sn, PADRE M. OROZCO ,P, Dp,Mz Rejas negras en la parte de afuera -78.66917,-1.645557,RB1P, , (-1.645557/-78.66917)</t>
+  </si>
+  <si>
     <t>VILLAGOMEZ BARRENO JESSICA KATHERINE</t>
   </si>
   <si>
@@ -159,6 +159,9 @@
     <t>ORDER/454877/2026</t>
   </si>
   <si>
+    <t>Quito, De Los Cipreses, COLLA LOMA DE LOS CIPRESES,S/N, DE LOS HELECHOS CONJ. IGUAZU 3,, ,S/N -78.4731063843,-0.126712814,PL2Q,KNAC9-3 , (-0.126712814/-78.4731063843)</t>
+  </si>
+  <si>
     <t>RAMOS GALARZA CARLOS ALBERTO</t>
   </si>
   <si>
@@ -168,6 +171,9 @@
     <t>ORDER/454819/2026</t>
   </si>
   <si>
+    <t>Ibarra, Rio Blanco, YACUCALLE RIO BLANCO,S/N, MIGUEL ALBAN PALIZ ,, , -78.12872,.3341155,IB1G,IBAC12 , (0.3341155/-78.12872)</t>
+  </si>
+  <si>
     <t>QUISHPE CHURTA FERNANDO ISRAEL</t>
   </si>
   <si>
@@ -177,6 +183,9 @@
     <t>ORDER/454817/2026</t>
   </si>
   <si>
+    <t>Ambato, Yahuira, LA VINCENTINA YAHUIRA,S/N, FRANCISCO FLOR ,, , CASA DE 3 PISOS COLOR BEIGE CON NARANJA -78.63076508,-1.2457316,AM5V,AMZC18 , (-1.2457316/-78.63076508)</t>
+  </si>
+  <si>
     <t>ALVAREZ MORALES DOMENICA ANAHI</t>
   </si>
   <si>
@@ -186,6 +195,9 @@
     <t>ORDER/454616/2026</t>
   </si>
   <si>
+    <t>Quito, La Concordia, (-0.098339/-78.434888)</t>
+  </si>
+  <si>
     <t>ALVAREZ CAOTILLO NATALIA ELIZABETH</t>
   </si>
   <si>
@@ -195,6 +207,9 @@
     <t>ORDER/454529/2026</t>
   </si>
   <si>
+    <t>Riobamba, Italia, VELOZ ITALIA,Villa Ns, ALBANIA ,P, Dp,Mz Casa de 3 pisos color verde porton negro -78.646164,-1.687489,RB4AM, , (-1.687489/-78.646164)</t>
+  </si>
+  <si>
     <t>LONDO CAIZA MARIA LAURA</t>
   </si>
   <si>
@@ -204,6 +219,9 @@
     <t>ORDER/454397/2026</t>
   </si>
   <si>
+    <t>Quito, Juan De Dios Martinez, BELLAVISTA JUAN DE DIOS MARTINEZ,N34-464, AV. PORTUGAL EDIF. TERRAZAS PORTELA,, , -78.4755249023,-.1823805273,BLL2AU,IQCC1-8 , (-0.1823805273/-78.4755249023)</t>
+  </si>
+  <si>
     <t>VILLACIS MEYTHALER ADRIANA LUCIA BEATRIZ</t>
   </si>
   <si>
@@ -213,6 +231,9 @@
     <t>ORDER/454337/2026</t>
   </si>
   <si>
+    <t>Cayambe, Bellavista, CAYAMBE BELLAVISTA,, INTI ,, , Casa de dos pisos color crema en el primer piso se encuentra a una tienda al lado del motel cicla -78.1343460083,.0377748907,CY2I, , (0.0377748907/-78.1343460083)</t>
+  </si>
+  <si>
     <t>MENDOZA QUIJIJE JOSTYN RICARDO</t>
   </si>
   <si>
@@ -222,6 +243,9 @@
     <t>ORDER/454274/2026</t>
   </si>
   <si>
+    <t>Quito, Bachiller Guevara, COTOCOLLAO BACHILLER GUEVARA,S/N, LIZARDO RUIZ ,S/N, SN,SN COLOR AZUL MILAGRO (17A) -78.49274437873541,-0.11364119476435827,CT5M,CTDB5-3,CT5M , (-0.11364119476435827/-78.49274437873541)</t>
+  </si>
+  <si>
     <t>VEGA CUEVA MARTHA TATIANA</t>
   </si>
   <si>
@@ -231,6 +255,9 @@
     <t>ORDER/454238/2026</t>
   </si>
   <si>
+    <t>Quito, Calle N44a, CONJ. JARDINES DEL BOSQUE PSJE. N44A,S/N, CALLE OE8 ,, , CONJ. JARDINES DEL BOSQUE CASA 28. FRANCISCO DE LA PITA S/N Y AV EL PARQUE -78.49934,-0.1595885,1H4A, , (-0.1595885/-78.49934)</t>
+  </si>
+  <si>
     <t>STANDBY MIGRA UIO ZM | ISERTEL (Tecnico)</t>
   </si>
   <si>
@@ -243,6 +270,9 @@
     <t>ORDER/454235/2026</t>
   </si>
   <si>
+    <t>Quito, Calle N44a, COCHAPAMBA SUR CALLE N44A,V. 16, CALLE OE8 CONJ. JARDINES DEL BOSQUE,, , CONJ. JARDINES DEL BOSQUE ATRAS DE JUGUETON -78.4994354248,-.1593364179,1H4A,1H4A , (-0.1593364179/-78.4994354248)</t>
+  </si>
+  <si>
     <t>ALMEIDA MARIN JANETTE LUCIA</t>
   </si>
   <si>
@@ -252,6 +282,9 @@
     <t>ORDER/454196/2026</t>
   </si>
   <si>
+    <t>Quito, Mercedes Pereda, EL RECREO MERCEDES PEREDA,S/N, FELIPE SANCHEZ ,, , CASA 3 PISOS CON PIEDRA VISTA Y CON DURAZNO CON PORTON NEGRO -78.520899,-.261359,9GC,9GC-3 , (-0.261359/-78.520899)</t>
+  </si>
+  <si>
     <t>ARELLANO SIMBA GALO VICENTE</t>
   </si>
   <si>
@@ -261,6 +294,9 @@
     <t>ORDER/453742/2026</t>
   </si>
   <si>
+    <t>Quito, Rumiurco, COTOCOLLAO RUMIURCO,V. 44, JOSE MARIA GUERRERO EDIF. SAN JAIME,, , CONJUNTO SAN JAIME 2 -78.4965133667,-.1189983264,1R,1R-4 , (-0.1189983264/-78.4965133667)</t>
+  </si>
+  <si>
     <t>ROMERO MONTENEGRO MARIA DEL CARMEN</t>
   </si>
   <si>
@@ -270,6 +306,9 @@
     <t>ORDER/453737/2026</t>
   </si>
   <si>
+    <t>Quito, Isabel Herreria, CHILLOGALLO ISABEL HERRERIA,S/N, JULIO JARA ,, , -78.56663,-0.2855736,MY1C,CHDC5-2 , (-0.2855736/-78.56663)</t>
+  </si>
+  <si>
     <t>Velasquez villarroel Lady lizbeth</t>
   </si>
   <si>
@@ -279,6 +318,9 @@
     <t>ORDER/453711/2026</t>
   </si>
   <si>
+    <t>Quito, Raul Padilla, BALCON DEL NORTE RAUL PADILLA,S/N, AV. MARISCAL SUCRE EDIF. QUANTUM,P. 1, DPTO. 4,S/N -78.48411,-.09448345,CL3BJ,CLGA15 , (-0.09448345/-78.48411)</t>
+  </si>
+  <si>
     <t>BALDEON FABARA ROBERTO JAVIER</t>
   </si>
   <si>
@@ -288,6 +330,9 @@
     <t>ORDER/453559/2026</t>
   </si>
   <si>
+    <t>Santo Domingo, Eduardo Galeano, COOP. ABDON CALDERON EDUARDO GALEANO,S/N, RUBEN DARIO ,, , -79.15494961285897,-0.25714629719490617,SC2W,SC2EC4,SC2W , (-0.25714629719490617/-79.15494961285897)</t>
+  </si>
+  <si>
     <t>PALACIOS HERNANDEZ MARCELO ELIESANDER</t>
   </si>
   <si>
@@ -297,6 +342,9 @@
     <t>ORDER/453432/2026</t>
   </si>
   <si>
+    <t>Quito, Calle Oe9a, EL BOSQUE CALLE OE9A,V. 211, AV. EL PARQUE ,P. 1, DPTO. 1-A, S/N -78.50023,-0.1632578,1H4C, , (-0.1632578/-78.50023)</t>
+  </si>
+  <si>
     <t>STANDBY MIGRA TV BOX UIO ZM | ISERTEL NORTE (Tecnico)</t>
   </si>
   <si>
@@ -309,6 +357,9 @@
     <t>ORDER/453415/2026</t>
   </si>
   <si>
+    <t>Quito, Av. Mariscal Sucre, SAN FERNANDO AV. MARISCAL SUCRE,, ANTONIO ROMAN CONJ. TORRES CONSTELACION,N51-151, DPTO. 203, -78.50041198,-.14477476,CT1AT,CMAF5-2 , (-0.14477476/-78.50041198)</t>
+  </si>
+  <si>
     <t>TOTTES CEVALLOS SAMYA LISETTE</t>
   </si>
   <si>
@@ -318,6 +369,9 @@
     <t>ORDER/453306/2026</t>
   </si>
   <si>
+    <t>Quito, Calle Oe11b, SANTA ROSA CALLE OE11B,, JOSE CHIRIBOGA ,, , CASA DE 3P COLOR CREMA CON GRIS EN EL PORTON -78.5602798462,-.2775941491,MY1R,CHCE1 , (-0.2775941491/-78.5602798462)</t>
+  </si>
+  <si>
     <t>ALMEIDA AREVALO JOSE ANTONIO</t>
   </si>
   <si>
@@ -327,6 +381,9 @@
     <t>ORDER/453273/2026</t>
   </si>
   <si>
+    <t>Quito, Av. Manuel Cordova Galarza, POMASQUI AV. MANUEL CORDOVA GALARZA,V. S3-35, SAN JOSE ,P. 2, S/N,S/N -78.45553,-0.05815028,QU2AC,PQEB1 , (-0.05815028/-78.45553)</t>
+  </si>
+  <si>
     <t>MEZA SILVA MARIA ESPERANZA</t>
   </si>
   <si>
@@ -336,6 +393,9 @@
     <t>ORDER/453266/2026</t>
   </si>
   <si>
+    <t>Quito, Vicente Heredia, CONJ. CIUDAD OCCIDENTE VICENTE HEREDIA,, ETAPA 3 COND. G,, DPTO. 301, -78.4996566772,-.1474287957,1CA,1CA-4 , (-0.1474287957/-78.4996566772)</t>
+  </si>
+  <si>
     <t>LOPEZ BUNDSCHUH JORGE LUIS</t>
   </si>
   <si>
@@ -345,6 +405,9 @@
     <t>ORDER/453143/2026</t>
   </si>
   <si>
+    <t>Quito, Vicente Heredia, CONJ. CIUDAD OCCIDENTE VICENTE HEREDIA,S/N, ETAPA 3 COND. H,P. 3, DPTO. 301, CERCA QUEDA LA GASOLINERA EL TERPEL -78.49948972,-0.14733090,1CA,1CA-4 , (-0.1473309/-78.49948972)</t>
+  </si>
+  <si>
     <t>MOSCOSO VALLEJO ZULEMA DEL CARMEN</t>
   </si>
   <si>
@@ -354,6 +417,9 @@
     <t>ORDER/452826/2026</t>
   </si>
   <si>
+    <t>Quito, Julio Cesar Villacres, BELLAVISTA JULIO CESAR VILLACRES,Villa B16, AV. MARISCAL SUCRE CONJ. PALERMO,P, Dp,Mz Conjunto Palermo casa B16 -78.507765,-.118654,CT6B,CNAC3-2 , (-0.118654/-78.507765)</t>
+  </si>
+  <si>
     <t>MOYON TACURI EDGAR FABIAN</t>
   </si>
   <si>
@@ -363,6 +429,9 @@
     <t>ORDER/452559/2026</t>
   </si>
   <si>
+    <t>Quito, Juan Barreiro, SOLANDA JUAN BARREIRO,Villa 1, CIPRIANO ALVARADO ,P, Dp,Mz Es de 3 pisos de baldosa verde y gris en la esquina hay una tienda vveres Anita -78.543958,-0.269286,MY6AD, , (-0.269286/-78.543958)</t>
+  </si>
+  <si>
     <t>BRIONES PONCE MILTON DAVID</t>
   </si>
   <si>
@@ -372,6 +441,9 @@
     <t>ORDER/452540/2026</t>
   </si>
   <si>
+    <t>Quito, Sabanilla, COTOCOLLAO SABANILLA,OE4-525, AV. DE LA PRENSA ,, , -78.494119,-0.120542,1R,1R-2 , (-0.120542/-78.494119)</t>
+  </si>
+  <si>
     <t>GUERRERO ALARCON CARLOS ALEJANDRO</t>
   </si>
   <si>
@@ -381,6 +453,9 @@
     <t>ORDER/452528/2026</t>
   </si>
   <si>
+    <t>Quito, Pedro Freile, COTOCOLLAO PEDRO FREILE,62-67, SABANILLA ,, , -78.49562,-0.12143104,1R, , (-0.12143104/-78.49562)</t>
+  </si>
+  <si>
     <t>LARREA MORILLO MARIA GABRIELA</t>
   </si>
   <si>
@@ -390,6 +465,9 @@
     <t>ORDER/451884/2026</t>
   </si>
   <si>
+    <t>Ambato, Antonio Clavijo, LA FLORESTA ANTONIO CLAVIJO,Villa SN, ISAIAS TORO RUIZ ,P, Dp,Mz Casa dos pisos color blanco -78.635915,-1.263194,AS1F, , (-1.263194/-78.635915)</t>
+  </si>
+  <si>
     <t>NUNEZ PAREDES IVETH NATALY</t>
   </si>
   <si>
@@ -399,6 +477,9 @@
     <t>ORDER/451232/2026</t>
   </si>
   <si>
+    <t>Quito, Jorge Piedra, ANDALUCIA JORGE PIEDRA,OE3-161, AV. DE LA PRENSA ,, , -78.493416,-.13901667,CT3AS,CPBG3 , (-0.13901667/-78.493416)</t>
+  </si>
+  <si>
     <t>LOPEZ GUERRA EZEQUIEL HERMOGENES</t>
   </si>
   <si>
@@ -408,6 +489,9 @@
     <t>ORDER/449997/2026</t>
   </si>
   <si>
+    <t>Santo Domingo, Romulo Betancour, COOP. ABDON CALDERON ROMULO BETANCOUR,V. SOLAR 23001, AV. LA LORENA ,P. 1, DPTO. 1,S/N ESQUINA DEL RESTURANTE LA PLAZA -79.15960819,-.25627349,SC2M,SC2CB9 , (-0.25627349/-79.15960819)</t>
+  </si>
+  <si>
     <t>LOOR BAUTISTA RASHELL JULIETH</t>
   </si>
   <si>
@@ -417,6 +501,9 @@
     <t>ORDER/450486/2026</t>
   </si>
   <si>
+    <t>Quito, Gonzalo Cordero, URB. EL CONDADO GONZALO CORDERO,OE5-61, CALLE B ,, , -78.4985046387,-.1005599871,CT6AU,CNAG3-9 , (-0.1005599871/-78.4985046387)</t>
+  </si>
+  <si>
     <t>CABRERA CHAVEZ LAURA MARIA</t>
   </si>
   <si>
@@ -426,6 +513,9 @@
     <t>ORDER/448988/2026</t>
   </si>
   <si>
+    <t>Cayambe, Olmedo, SAN PEDRO OLMEDO,S/N, VARGAS ,, , -78.140529,.041851,CY3U,CYEB4-3 , (0.041851/-78.140529)</t>
+  </si>
+  <si>
     <t>Valladares Espinosa Maria Augusta</t>
   </si>
   <si>
@@ -435,12 +525,18 @@
     <t>ORDER/446561/2026</t>
   </si>
   <si>
+    <t>Quito, Av. Eloy Alfaro, BATAN AV. ELOY ALFARO,V. N35-09, PORTUGAL EDIF. MILENIUM PLAZA,P. 4, DPTO. 401, -78.4756,-.181343,2B1B,2B1B , (-0.181343/-78.4756)</t>
+  </si>
+  <si>
     <t>TASK/520585/2026</t>
   </si>
   <si>
     <t>ORDER/441349/2026</t>
   </si>
   <si>
+    <t>Latacunga, Salcedo, SAN FELIPE SALCEDO,Villa Sn, GUAYTACAMA ,P, Dp,Mz Casa de tres pisos color melon -78.624438,-0.930242,LT2K, , (-0.930242/-78.624438)</t>
+  </si>
+  <si>
     <t>ISERAMB-10 LAT GPON Z2 | SIVINTA ALMACHI JUAN (Tecnico)</t>
   </si>
   <si>
@@ -453,6 +549,9 @@
     <t>ORDER/444572/2026</t>
   </si>
   <si>
+    <t>Quito, Los Cabildos, QUITO TENNIS LOS CABILDOS,V. N40-275, DE LAS ALMONEDAS EDIF. MALAGA,P. 1, DPTO. 1, -78.49496,-.1663396,1FA,1FA-1 , (-0.1663396/-78.49496)</t>
+  </si>
+  <si>
     <t>RAMOS CORDOVA VERONICA DE LOS ANG</t>
   </si>
   <si>
@@ -460,6 +559,9 @@
   </si>
   <si>
     <t>ORDER/429464/2026</t>
+  </si>
+  <si>
+    <t>Riobamba, Colombia, BONILLA ABARCA COLOMBIA,# 37-31, BRASIL ,, , //FRENTE DEL HOSPITAL DEL IESS CASA DE 2 PISOS COLOR CAFE -78.65917,-1.669559,RB3AJ,RIGB18 , (-1.669559/-78.65917)</t>
   </si>
   <si>
     <t>MORALES MERCHAN MARCELO FABIAN</t>
@@ -863,19 +965,19 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -884,31 +986,31 @@
         <v>1</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2">
         <v>11410416</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G2" s="3">
         <v>46288.333333333336</v>
@@ -919,22 +1021,22 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2">
         <v>11688540</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G3" s="3">
         <v>46288.416666666664</v>
@@ -945,22 +1047,22 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
         <v>36</v>
       </c>
-      <c r="B4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E4" s="2">
         <v>5703275</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" s="3">
         <v>46288.583333333336</v>
@@ -971,16 +1073,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s">
         <v>39</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2">
         <v>11688794</v>
@@ -1002,17 +1104,17 @@
       <c r="B6" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="E6" s="2">
         <v>7885764</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" s="3">
         <v>46288.75</v>
@@ -1023,22 +1125,22 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="E7" s="2">
         <v>9764924</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G7" s="3">
         <v>46288.5</v>
@@ -1049,22 +1151,22 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2">
         <v>11434248</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G8" s="3">
         <v>46288.333333333336</v>
@@ -1075,22 +1177,22 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>4</v>
+        <v>55</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E9" s="2">
         <v>11688496</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G9" s="3">
         <v>46288.333333333336</v>
@@ -1101,22 +1203,22 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>15</v>
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2">
         <v>11688657</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G10" s="3">
         <v>46288.333333333336</v>
@@ -1127,22 +1229,22 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>4</v>
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2">
         <v>9687294</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G11" s="3">
         <v>46288.583333333336</v>
@@ -1153,22 +1255,22 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>4</v>
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E12" s="2">
         <v>11649135</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G12" s="3">
         <v>46288.333333333336</v>
@@ -1179,22 +1281,22 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>4</v>
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E13" s="2">
         <v>5507511</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G13" s="3">
         <v>46288.333333333336</v>
@@ -1205,22 +1307,22 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>4</v>
+        <v>75</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E14" s="2">
         <v>5032094</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G14" s="3">
         <v>46288.583333333336</v>
@@ -1231,22 +1333,22 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
+        <v>80</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E15" s="2">
         <v>5551700</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="G15" s="3">
         <v>46288.5</v>
@@ -1257,22 +1359,22 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>4</v>
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
+        <v>85</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E16" s="2">
         <v>11627175</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="G16" s="3">
         <v>46288.333333333336</v>
@@ -1283,22 +1385,22 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>4</v>
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E17" s="2">
         <v>4801348</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G17" s="3">
         <v>46288.583333333336</v>
@@ -1309,22 +1411,22 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>4</v>
+        <v>92</v>
+      </c>
+      <c r="C18" t="s">
+        <v>93</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2">
         <v>9115188</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G18" s="3">
         <v>46288.583333333336</v>
@@ -1335,22 +1437,22 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>4</v>
+        <v>96</v>
+      </c>
+      <c r="C19" t="s">
+        <v>97</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E19" s="2">
         <v>9486426</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="G19" s="3">
         <v>46288.333333333336</v>
@@ -1361,22 +1463,22 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="C20" t="s">
+        <v>101</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2">
         <v>5027587</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="G20" s="3">
         <v>46288.416666666664</v>
@@ -1387,22 +1489,22 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>4</v>
+        <v>104</v>
+      </c>
+      <c r="C21" t="s">
+        <v>105</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="E21" s="2">
         <v>4300590</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G21" s="3">
         <v>46288.333333333336</v>
@@ -1413,22 +1515,22 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>4</v>
+        <v>109</v>
+      </c>
+      <c r="C22" t="s">
+        <v>110</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E22" s="2">
         <v>9062999</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="G22" s="3">
         <v>46288.75</v>
@@ -1439,22 +1541,22 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>4</v>
+        <v>113</v>
+      </c>
+      <c r="C23" t="s">
+        <v>114</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E23" s="2">
         <v>1466337</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="G23" s="3">
         <v>46288.333333333336</v>
@@ -1465,22 +1567,22 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>4</v>
+        <v>117</v>
+      </c>
+      <c r="C24" t="s">
+        <v>118</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E24" s="2">
         <v>8983724</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="G24" s="3">
         <v>46288.333333333336</v>
@@ -1491,22 +1593,22 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>4</v>
+        <v>121</v>
+      </c>
+      <c r="C25" t="s">
+        <v>122</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="E25" s="2">
         <v>4932445</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="G25" s="3">
         <v>46288.583333333336</v>
@@ -1517,22 +1619,22 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>4</v>
+        <v>125</v>
+      </c>
+      <c r="C26" t="s">
+        <v>126</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="E26" s="2">
         <v>6034380</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="G26" s="3">
         <v>46288.666666666664</v>
@@ -1543,22 +1645,22 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>4</v>
+        <v>129</v>
+      </c>
+      <c r="C27" t="s">
+        <v>130</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E27" s="2">
         <v>11666607</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="G27" s="3">
         <v>46288.666666666664</v>
@@ -1569,22 +1671,22 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>4</v>
+        <v>133</v>
+      </c>
+      <c r="C28" t="s">
+        <v>134</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E28" s="2">
         <v>11688223</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="G28" s="3">
         <v>46288.416666666664</v>
@@ -1595,22 +1697,22 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>4</v>
+        <v>137</v>
+      </c>
+      <c r="C29" t="s">
+        <v>138</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E29" s="2">
         <v>6091803</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="G29" s="3">
         <v>46288.583333333336</v>
@@ -1621,22 +1723,22 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>4</v>
+        <v>141</v>
+      </c>
+      <c r="C30" t="s">
+        <v>142</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E30" s="2">
         <v>4845399</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="G30" s="3">
         <v>46288.666666666664</v>
@@ -1647,22 +1749,22 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>7</v>
+        <v>145</v>
+      </c>
+      <c r="C31" t="s">
+        <v>146</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E31" s="2">
         <v>11687954</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="G31" s="3">
         <v>46288.416666666664</v>
@@ -1673,22 +1775,22 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="B32" t="s">
-        <v>123</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>4</v>
+        <v>149</v>
+      </c>
+      <c r="C32" t="s">
+        <v>150</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E32" s="2">
         <v>5522748</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="G32" s="3">
         <v>46288.666666666664</v>
@@ -1699,22 +1801,22 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>4</v>
+        <v>153</v>
+      </c>
+      <c r="C33" t="s">
+        <v>154</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2">
         <v>11157458</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="G33" s="3">
         <v>46288.333333333336</v>
@@ -1725,22 +1827,22 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="B34" t="s">
-        <v>129</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>4</v>
+        <v>157</v>
+      </c>
+      <c r="C34" t="s">
+        <v>158</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E34" s="2">
         <v>5005428</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="G34" s="3">
         <v>46288.333333333336</v>
@@ -1751,22 +1853,22 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>4</v>
+        <v>161</v>
+      </c>
+      <c r="C35" t="s">
+        <v>162</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E35" s="2">
         <v>10978451</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="G35" s="3">
         <v>46288.416666666664</v>
@@ -1777,16 +1879,16 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>4</v>
+        <v>165</v>
+      </c>
+      <c r="C36" t="s">
+        <v>166</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E36" s="2">
         <v>7600082</v>
@@ -1801,22 +1903,22 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>4</v>
+        <v>23</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E37" s="2">
         <v>8862018</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G37" s="3">
         <v>46287.416666666664</v>
@@ -1827,22 +1929,22 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>7</v>
+        <v>168</v>
+      </c>
+      <c r="C38" t="s">
+        <v>169</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="E38" s="2">
         <v>4803583</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>139</v>
+        <v>171</v>
       </c>
       <c r="G38" s="3">
         <v>46288.333333333336</v>
@@ -1853,22 +1955,22 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="B39" t="s">
-        <v>141</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>4</v>
+        <v>173</v>
+      </c>
+      <c r="C39" t="s">
+        <v>174</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="E39" s="2">
         <v>5038624</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="G39" s="3">
         <v>46288.416666666664</v>
@@ -1879,22 +1981,22 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="B40" t="s">
-        <v>144</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>15</v>
+        <v>177</v>
+      </c>
+      <c r="C40" t="s">
+        <v>178</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E40" s="2">
         <v>12634</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="G40" s="3">
         <v>46288.333333333336</v>

--- a/docs/base_datos.xlsx
+++ b/docs/base_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9cd9fa3079768ea/Desktop/CONFIRMACION PREVIA/backend/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{A069D832-941B-4A69-9AFD-A62A51A2887A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99BEC59D-7659-48A4-8CB1-F59397920035}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{A069D832-941B-4A69-9AFD-A62A51A2887A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FD679D3-B49F-4357-A885-58BAF9DB5BC2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{203DBCE0-566D-42E5-8A51-BDC7143FE5DE}"/>
   </bookViews>
@@ -30,9 +30,6 @@
     <t> Cliente</t>
   </si>
   <si>
-    <t> Fecha de programación desde</t>
-  </si>
-  <si>
     <t>ISERIBA-38 MANTE IBA GPON Z0 | UMAQUINGA CRIOLLO MATEO GABRIEL (Tecnico)</t>
   </si>
   <si>
@@ -586,6 +583,9 @@
   </si>
   <si>
     <t>CONTRATO</t>
+  </si>
+  <si>
+    <t> Fecha de programación</t>
   </si>
 </sst>
 </file>
@@ -965,52 +965,52 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>185</v>
       </c>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2">
         <v>11410416</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2" s="3">
         <v>46288.333333333336</v>
@@ -1021,22 +1021,22 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
         <v>30</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>31</v>
       </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2">
         <v>11688540</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3" s="3">
         <v>46288.416666666664</v>
@@ -1047,22 +1047,22 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>35</v>
       </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2">
         <v>5703275</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4" s="3">
         <v>46288.583333333336</v>
@@ -1073,22 +1073,22 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
         <v>38</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>39</v>
       </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2">
         <v>11688794</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" s="3">
         <v>46288.416666666664</v>
@@ -1099,22 +1099,22 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
         <v>42</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>43</v>
       </c>
-      <c r="C6" t="s">
-        <v>44</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2">
         <v>7885764</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G6" s="3">
         <v>46288.75</v>
@@ -1125,22 +1125,22 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
         <v>46</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>47</v>
       </c>
-      <c r="C7" t="s">
-        <v>48</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2">
         <v>9764924</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G7" s="3">
         <v>46288.5</v>
@@ -1151,22 +1151,22 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
         <v>50</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>51</v>
       </c>
-      <c r="C8" t="s">
-        <v>52</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2">
         <v>11434248</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G8" s="3">
         <v>46288.333333333336</v>
@@ -1177,22 +1177,22 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
         <v>54</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>55</v>
       </c>
-      <c r="C9" t="s">
-        <v>56</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2">
         <v>11688496</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9" s="3">
         <v>46288.333333333336</v>
@@ -1203,22 +1203,22 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
         <v>58</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>59</v>
       </c>
-      <c r="C10" t="s">
-        <v>60</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2">
         <v>11688657</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G10" s="3">
         <v>46288.333333333336</v>
@@ -1229,22 +1229,22 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s">
         <v>62</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>63</v>
       </c>
-      <c r="C11" t="s">
-        <v>64</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" s="2">
         <v>9687294</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G11" s="3">
         <v>46288.583333333336</v>
@@ -1255,22 +1255,22 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
         <v>66</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="C12" t="s">
-        <v>68</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2">
         <v>11649135</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G12" s="3">
         <v>46288.333333333336</v>
@@ -1281,22 +1281,22 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
         <v>70</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>71</v>
       </c>
-      <c r="C13" t="s">
-        <v>72</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" s="2">
         <v>5507511</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G13" s="3">
         <v>46288.333333333336</v>
@@ -1307,22 +1307,22 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
         <v>74</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>75</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="E14" s="2">
         <v>5032094</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G14" s="3">
         <v>46288.583333333336</v>
@@ -1333,22 +1333,22 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s">
         <v>79</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>80</v>
       </c>
-      <c r="C15" t="s">
-        <v>81</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E15" s="2">
         <v>5551700</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G15" s="3">
         <v>46288.5</v>
@@ -1359,22 +1359,22 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" t="s">
         <v>83</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>84</v>
       </c>
-      <c r="C16" t="s">
-        <v>85</v>
-      </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="2">
         <v>11627175</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G16" s="3">
         <v>46288.333333333336</v>
@@ -1385,22 +1385,22 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
         <v>87</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>88</v>
       </c>
-      <c r="C17" t="s">
-        <v>89</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" s="2">
         <v>4801348</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G17" s="3">
         <v>46288.583333333336</v>
@@ -1411,22 +1411,22 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
         <v>91</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>92</v>
       </c>
-      <c r="C18" t="s">
-        <v>93</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2">
         <v>9115188</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G18" s="3">
         <v>46288.583333333336</v>
@@ -1437,22 +1437,22 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" t="s">
         <v>95</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>96</v>
       </c>
-      <c r="C19" t="s">
-        <v>97</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="2">
         <v>9486426</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G19" s="3">
         <v>46288.333333333336</v>
@@ -1463,22 +1463,22 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" t="s">
         <v>99</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>100</v>
       </c>
-      <c r="C20" t="s">
-        <v>101</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" s="2">
         <v>5027587</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G20" s="3">
         <v>46288.416666666664</v>
@@ -1489,22 +1489,22 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" t="s">
         <v>103</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>104</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="E21" s="2">
         <v>4300590</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G21" s="3">
         <v>46288.333333333336</v>
@@ -1515,22 +1515,22 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" t="s">
         <v>108</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>109</v>
       </c>
-      <c r="C22" t="s">
-        <v>110</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E22" s="2">
         <v>9062999</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G22" s="3">
         <v>46288.75</v>
@@ -1541,22 +1541,22 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" t="s">
         <v>112</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>113</v>
       </c>
-      <c r="C23" t="s">
-        <v>114</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E23" s="2">
         <v>1466337</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G23" s="3">
         <v>46288.333333333336</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" t="s">
         <v>116</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>117</v>
       </c>
-      <c r="C24" t="s">
-        <v>118</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2">
         <v>8983724</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G24" s="3">
         <v>46288.333333333336</v>
@@ -1593,22 +1593,22 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25" t="s">
         <v>120</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>121</v>
       </c>
-      <c r="C25" t="s">
-        <v>122</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E25" s="2">
         <v>4932445</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G25" s="3">
         <v>46288.583333333336</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" t="s">
         <v>124</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>125</v>
       </c>
-      <c r="C26" t="s">
-        <v>126</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E26" s="2">
         <v>6034380</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G26" s="3">
         <v>46288.666666666664</v>
@@ -1645,22 +1645,22 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" t="s">
         <v>128</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>129</v>
       </c>
-      <c r="C27" t="s">
-        <v>130</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E27" s="2">
         <v>11666607</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G27" s="3">
         <v>46288.666666666664</v>
@@ -1671,22 +1671,22 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" t="s">
         <v>132</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>133</v>
       </c>
-      <c r="C28" t="s">
-        <v>134</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2">
         <v>11688223</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G28" s="3">
         <v>46288.416666666664</v>
@@ -1697,22 +1697,22 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>135</v>
+      </c>
+      <c r="B29" t="s">
         <v>136</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>137</v>
       </c>
-      <c r="C29" t="s">
-        <v>138</v>
-      </c>
       <c r="D29" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E29" s="2">
         <v>6091803</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G29" s="3">
         <v>46288.583333333336</v>
@@ -1723,22 +1723,22 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>139</v>
+      </c>
+      <c r="B30" t="s">
         <v>140</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>141</v>
       </c>
-      <c r="C30" t="s">
-        <v>142</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E30" s="2">
         <v>4845399</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G30" s="3">
         <v>46288.666666666664</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B31" t="s">
         <v>144</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>145</v>
       </c>
-      <c r="C31" t="s">
-        <v>146</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31" s="2">
         <v>11687954</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G31" s="3">
         <v>46288.416666666664</v>
@@ -1775,22 +1775,22 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B32" t="s">
         <v>148</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>149</v>
       </c>
-      <c r="C32" t="s">
-        <v>150</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E32" s="2">
         <v>5522748</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G32" s="3">
         <v>46288.666666666664</v>
@@ -1801,22 +1801,22 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" t="s">
         <v>152</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>153</v>
       </c>
-      <c r="C33" t="s">
-        <v>154</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E33" s="2">
         <v>11157458</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G33" s="3">
         <v>46288.333333333336</v>
@@ -1827,22 +1827,22 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>155</v>
+      </c>
+      <c r="B34" t="s">
         <v>156</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>157</v>
       </c>
-      <c r="C34" t="s">
-        <v>158</v>
-      </c>
       <c r="D34" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E34" s="2">
         <v>5005428</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G34" s="3">
         <v>46288.333333333336</v>
@@ -1853,22 +1853,22 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>159</v>
+      </c>
+      <c r="B35" t="s">
         <v>160</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>161</v>
       </c>
-      <c r="C35" t="s">
-        <v>162</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E35" s="2">
         <v>10978451</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G35" s="3">
         <v>46288.416666666664</v>
@@ -1879,16 +1879,16 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>163</v>
+      </c>
+      <c r="B36" t="s">
         <v>164</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>165</v>
       </c>
-      <c r="C36" t="s">
-        <v>166</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E36" s="2">
         <v>7600082</v>
@@ -1903,22 +1903,22 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" t="s">
         <v>22</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>23</v>
       </c>
-      <c r="C37" t="s">
-        <v>24</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E37" s="2">
         <v>8862018</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G37" s="3">
         <v>46287.416666666664</v>
@@ -1929,22 +1929,22 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>166</v>
+      </c>
+      <c r="B38" t="s">
         <v>167</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>168</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="E38" s="2">
         <v>4803583</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G38" s="3">
         <v>46288.333333333336</v>
@@ -1955,22 +1955,22 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>171</v>
+      </c>
+      <c r="B39" t="s">
         <v>172</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>173</v>
       </c>
-      <c r="C39" t="s">
-        <v>174</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E39" s="2">
         <v>5038624</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G39" s="3">
         <v>46288.416666666664</v>
@@ -1981,22 +1981,22 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>175</v>
+      </c>
+      <c r="B40" t="s">
         <v>176</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>177</v>
       </c>
-      <c r="C40" t="s">
-        <v>178</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E40" s="2">
         <v>12634</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G40" s="3">
         <v>46288.333333333336</v>

--- a/docs/base_datos.xlsx
+++ b/docs/base_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9cd9fa3079768ea/Desktop/CONFIRMACION PREVIA/backend/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{A069D832-941B-4A69-9AFD-A62A51A2887A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FD679D3-B49F-4357-A885-58BAF9DB5BC2}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{A069D832-941B-4A69-9AFD-A62A51A2887A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B1F5EEF-C81D-4068-A795-8631869F0948}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{203DBCE0-566D-42E5-8A51-BDC7143FE5DE}"/>
   </bookViews>

--- a/docs/base_datos.xlsx
+++ b/docs/base_datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9cd9fa3079768ea/Desktop/CONFIRMACION PREVIA/backend/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{A069D832-941B-4A69-9AFD-A62A51A2887A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B1F5EEF-C81D-4068-A795-8631869F0948}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{A069D832-941B-4A69-9AFD-A62A51A2887A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F40ED935-D76F-4E92-A3DD-051BD3705C8F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{203DBCE0-566D-42E5-8A51-BDC7143FE5DE}"/>
   </bookViews>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="187">
   <si>
-    <t> Cliente</t>
-  </si>
-  <si>
     <t>ISERIBA-38 MANTE IBA GPON Z0 | UMAQUINGA CRIOLLO MATEO GABRIEL (Tecnico)</t>
   </si>
   <si>
@@ -576,16 +573,19 @@
     <t>TECNICO</t>
   </si>
   <si>
-    <t>Operador</t>
-  </si>
-  <si>
-    <t>Observacion</t>
-  </si>
-  <si>
     <t>CONTRATO</t>
   </si>
   <si>
-    <t> Fecha de programación</t>
+    <t> CLIENTE</t>
+  </si>
+  <si>
+    <t>FECHA DE PROGRAMACIÓN</t>
+  </si>
+  <si>
+    <t>OPERADOR</t>
+  </si>
+  <si>
+    <t>OBSERVACION</t>
   </si>
 </sst>
 </file>
@@ -965,52 +965,52 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>26</v>
       </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2">
         <v>11410416</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2" s="3">
         <v>46288.333333333336</v>
@@ -1021,22 +1021,22 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2">
         <v>11688540</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3" s="3">
         <v>46288.416666666664</v>
@@ -1047,22 +1047,22 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>34</v>
       </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2">
         <v>5703275</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G4" s="3">
         <v>46288.583333333336</v>
@@ -1073,22 +1073,22 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
         <v>37</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>38</v>
       </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2">
         <v>11688794</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" s="3">
         <v>46288.416666666664</v>
@@ -1099,22 +1099,22 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
         <v>41</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>42</v>
       </c>
-      <c r="C6" t="s">
-        <v>43</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2">
         <v>7885764</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G6" s="3">
         <v>46288.75</v>
@@ -1125,22 +1125,22 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
         <v>45</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>46</v>
       </c>
-      <c r="C7" t="s">
-        <v>47</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2">
         <v>9764924</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G7" s="3">
         <v>46288.5</v>
@@ -1151,22 +1151,22 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
         <v>49</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>50</v>
       </c>
-      <c r="C8" t="s">
-        <v>51</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2">
         <v>11434248</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8" s="3">
         <v>46288.333333333336</v>
@@ -1177,22 +1177,22 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
         <v>53</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>54</v>
       </c>
-      <c r="C9" t="s">
-        <v>55</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" s="2">
         <v>11688496</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9" s="3">
         <v>46288.333333333336</v>
@@ -1203,22 +1203,22 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
         <v>57</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>58</v>
       </c>
-      <c r="C10" t="s">
-        <v>59</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" s="2">
         <v>11688657</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10" s="3">
         <v>46288.333333333336</v>
@@ -1229,22 +1229,22 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
         <v>61</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>62</v>
       </c>
-      <c r="C11" t="s">
-        <v>63</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2">
         <v>9687294</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G11" s="3">
         <v>46288.583333333336</v>
@@ -1255,22 +1255,22 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
         <v>65</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>66</v>
       </c>
-      <c r="C12" t="s">
-        <v>67</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2">
         <v>11649135</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G12" s="3">
         <v>46288.333333333336</v>
@@ -1281,22 +1281,22 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s">
         <v>69</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>70</v>
       </c>
-      <c r="C13" t="s">
-        <v>71</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2">
         <v>5507511</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G13" s="3">
         <v>46288.333333333336</v>
@@ -1307,22 +1307,22 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" t="s">
         <v>73</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>74</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="E14" s="2">
         <v>5032094</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G14" s="3">
         <v>46288.583333333336</v>
@@ -1333,22 +1333,22 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" t="s">
         <v>78</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>79</v>
       </c>
-      <c r="C15" t="s">
-        <v>80</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E15" s="2">
         <v>5551700</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G15" s="3">
         <v>46288.5</v>
@@ -1359,22 +1359,22 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" t="s">
         <v>82</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>83</v>
       </c>
-      <c r="C16" t="s">
-        <v>84</v>
-      </c>
       <c r="D16" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="2">
         <v>11627175</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G16" s="3">
         <v>46288.333333333336</v>
@@ -1385,22 +1385,22 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" t="s">
         <v>86</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>87</v>
       </c>
-      <c r="C17" t="s">
-        <v>88</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="2">
         <v>4801348</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G17" s="3">
         <v>46288.583333333336</v>
@@ -1411,22 +1411,22 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
         <v>90</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>91</v>
       </c>
-      <c r="C18" t="s">
-        <v>92</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="2">
         <v>9115188</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G18" s="3">
         <v>46288.583333333336</v>
@@ -1437,22 +1437,22 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" t="s">
         <v>94</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>95</v>
       </c>
-      <c r="C19" t="s">
-        <v>96</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="2">
         <v>9486426</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G19" s="3">
         <v>46288.333333333336</v>
@@ -1463,22 +1463,22 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" t="s">
         <v>98</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>99</v>
       </c>
-      <c r="C20" t="s">
-        <v>100</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" s="2">
         <v>5027587</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
         <v>46288.416666666664</v>
@@ -1489,22 +1489,22 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" t="s">
         <v>102</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>103</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="E21" s="2">
         <v>4300590</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G21" s="3">
         <v>46288.333333333336</v>
@@ -1515,22 +1515,22 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" t="s">
         <v>107</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>108</v>
       </c>
-      <c r="C22" t="s">
-        <v>109</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E22" s="2">
         <v>9062999</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G22" s="3">
         <v>46288.75</v>
@@ -1541,22 +1541,22 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" t="s">
         <v>111</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>112</v>
       </c>
-      <c r="C23" t="s">
-        <v>113</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E23" s="2">
         <v>1466337</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G23" s="3">
         <v>46288.333333333336</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" t="s">
         <v>115</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>116</v>
       </c>
-      <c r="C24" t="s">
-        <v>117</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E24" s="2">
         <v>8983724</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G24" s="3">
         <v>46288.333333333336</v>
@@ -1593,22 +1593,22 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" t="s">
         <v>119</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>120</v>
       </c>
-      <c r="C25" t="s">
-        <v>121</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E25" s="2">
         <v>4932445</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G25" s="3">
         <v>46288.583333333336</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" t="s">
         <v>123</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>124</v>
       </c>
-      <c r="C26" t="s">
-        <v>125</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E26" s="2">
         <v>6034380</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G26" s="3">
         <v>46288.666666666664</v>
@@ -1645,22 +1645,22 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" t="s">
         <v>127</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>128</v>
       </c>
-      <c r="C27" t="s">
-        <v>129</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E27" s="2">
         <v>11666607</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G27" s="3">
         <v>46288.666666666664</v>
@@ -1671,22 +1671,22 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B28" t="s">
         <v>131</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>132</v>
       </c>
-      <c r="C28" t="s">
-        <v>133</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28" s="2">
         <v>11688223</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G28" s="3">
         <v>46288.416666666664</v>
@@ -1697,22 +1697,22 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>134</v>
+      </c>
+      <c r="B29" t="s">
         <v>135</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>136</v>
       </c>
-      <c r="C29" t="s">
-        <v>137</v>
-      </c>
       <c r="D29" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E29" s="2">
         <v>6091803</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G29" s="3">
         <v>46288.583333333336</v>
@@ -1723,22 +1723,22 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" t="s">
         <v>139</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>140</v>
       </c>
-      <c r="C30" t="s">
-        <v>141</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E30" s="2">
         <v>4845399</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G30" s="3">
         <v>46288.666666666664</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>142</v>
+      </c>
+      <c r="B31" t="s">
         <v>143</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>144</v>
       </c>
-      <c r="C31" t="s">
-        <v>145</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" s="2">
         <v>11687954</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G31" s="3">
         <v>46288.416666666664</v>
@@ -1775,22 +1775,22 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>146</v>
+      </c>
+      <c r="B32" t="s">
         <v>147</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>148</v>
       </c>
-      <c r="C32" t="s">
-        <v>149</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E32" s="2">
         <v>5522748</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G32" s="3">
         <v>46288.666666666664</v>
@@ -1801,22 +1801,22 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>150</v>
+      </c>
+      <c r="B33" t="s">
         <v>151</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>152</v>
       </c>
-      <c r="C33" t="s">
-        <v>153</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E33" s="2">
         <v>11157458</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G33" s="3">
         <v>46288.333333333336</v>
@@ -1827,22 +1827,22 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>154</v>
+      </c>
+      <c r="B34" t="s">
         <v>155</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>156</v>
       </c>
-      <c r="C34" t="s">
-        <v>157</v>
-      </c>
       <c r="D34" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E34" s="2">
         <v>5005428</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G34" s="3">
         <v>46288.333333333336</v>
@@ -1853,22 +1853,22 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>158</v>
+      </c>
+      <c r="B35" t="s">
         <v>159</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>160</v>
       </c>
-      <c r="C35" t="s">
-        <v>161</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E35" s="2">
         <v>10978451</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G35" s="3">
         <v>46288.416666666664</v>
@@ -1879,16 +1879,16 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>162</v>
+      </c>
+      <c r="B36" t="s">
         <v>163</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>164</v>
       </c>
-      <c r="C36" t="s">
-        <v>165</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E36" s="2">
         <v>7600082</v>
@@ -1903,22 +1903,22 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" t="s">
         <v>21</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>22</v>
       </c>
-      <c r="C37" t="s">
-        <v>23</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E37" s="2">
         <v>8862018</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G37" s="3">
         <v>46287.416666666664</v>
@@ -1929,22 +1929,22 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>165</v>
+      </c>
+      <c r="B38" t="s">
         <v>166</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>167</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="E38" s="2">
         <v>4803583</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G38" s="3">
         <v>46288.333333333336</v>
@@ -1955,22 +1955,22 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>170</v>
+      </c>
+      <c r="B39" t="s">
         <v>171</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>172</v>
       </c>
-      <c r="C39" t="s">
-        <v>173</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E39" s="2">
         <v>5038624</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G39" s="3">
         <v>46288.416666666664</v>
@@ -1981,22 +1981,22 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" t="s">
         <v>175</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>176</v>
       </c>
-      <c r="C40" t="s">
-        <v>177</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E40" s="2">
         <v>12634</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G40" s="3">
         <v>46288.333333333336</v>
